--- a/Data Files/fixtures/CCIPH-58/valid_actuals.xlsx
+++ b/Data Files/fixtures/CCIPH-58/valid_actuals.xlsx
@@ -67,7 +67,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>300</t>
+    <t>100</t>
   </si>
   <si>
     <t>0</t>
